--- a/sampleprojects/TaxReturn/excel/states/IL.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IL.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>DT: il tax</t>
   </si>
@@ -137,7 +137,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(13 attributes)</t>
+    <t>(12 attributes)</t>
   </si>
   <si>
     <t>il_adjusted_agi</t>
@@ -231,12 +231,6 @@
   </si>
   <si>
     <t>Illinois uses federal adjusted gross income as starting point, with specific additions and subtractions per 35 ILCS 5/203(b)(1). Illinois does not have a state standard deduction.</t>
-  </si>
-  <si>
-    <t>state_tax_liability</t>
-  </si>
-  <si>
-    <t>Illinois state tax liability (computed). IL taxable income × 4.95% flat rate per 35 ILCS 5/201(b)</t>
   </si>
 </sst>
 </file>
@@ -1859,47 +1853,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>